--- a/合同全生命周期管理系统-项目管理套件/90_项目数据中心/项目计划基线-20260917-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/90_项目数据中心/项目计划基线-20260917-V1.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="6" r:id="R950f24c002ba4cc7"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目阶段" sheetId="1" r:id="Rd0c1e8da2e8b46f5"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑" sheetId="2" r:id="R892a6d0abdb04f7d"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WBS" sheetId="3" r:id="R7160def65550449c"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="角色编制" sheetId="4" r:id="R9101e3d9a0b14cb8"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="阶段资源" sheetId="5" r:id="R20ea3581b0a347da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="使用说明" sheetId="6" r:id="R950f24c002ba4cc7"/>
   </x:sheets>
 </x:workbook>
 </file>
